--- a/records/成大第一階段辨識問卷_1150304建議修改版.xlsx
+++ b/records/成大第一階段辨識問卷_1150304建議修改版.xlsx
@@ -1208,59 +1208,118 @@
       </c>
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="n"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>000005_raw.jpg</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="0" t="inlineStr">
         <is>
           <t>"健亞"  健得靜錠０．２５毫克（三氮二氮平）</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="0" t="inlineStr">
         <is>
           <t>"中國化學" 安蒙西林膠囊500毫克</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="0" t="inlineStr">
         <is>
           <t>"健亞"  健得靜錠０．２５毫克（三氮二氮平）</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="0" t="inlineStr">
         <is>
           <t>"井田"舒管錠2.5毫克(硫酸特必林)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="0" t="inlineStr">
         <is>
           <t>"健亞"  健得靜錠０．２５毫克（三氮二氮平）</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="0" t="inlineStr">
         <is>
           <t>朗斯弗膜衣錠15毫克</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20.1" customHeight="1" s="13">
-      <c r="A10" s="5" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>000006</t>
+        </is>
+      </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>第1階段</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/27</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>正確</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>正確</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>正確</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>正確</t>
+        </is>
+      </c>
       <c r="K10" s="5" t="n"/>
       <c r="L10" s="5" t="n"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>000006_raw.jpg</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Demo Drug 1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Demo Drug 2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Demo Drug 3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Demo Drug 4</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Demo Drug 5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Demo Drug 6</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20.1" customHeight="1" s="13">
       <c r="A11" s="5" t="n"/>
